--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484772_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484772_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0943</v>
+        <v>7.6798</v>
       </c>
       <c r="E2" t="n">
-        <v>9.907</v>
+        <v>10.8628</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8126</v>
+        <v>-3.183</v>
       </c>
       <c r="G2" t="n">
         <v>9.5032</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6542</v>
+        <v>-1.0687</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6802</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.026</v>
+        <v>-0.3444</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9434</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3519</v>
+        <v>3.1561</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2349</v>
+        <v>2.6602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.117</v>
+        <v>0.4959</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.3016</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.5108</v>
+        <v>0.5079</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4223</v>
+        <v>-0.8096</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7447</v>
+        <v>0.5073</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.3698</v>
+        <v>1.4689</v>
       </c>
       <c r="L3" t="n">
-        <v>4.1145</v>
+        <v>-0.9616</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8331</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.141</v>
+        <v>-0.961</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6922</v>
+        <v>0.152</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1322</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4403</v>
+        <v>-0.7308</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1509</v>
+        <v>-0.4505</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2894</v>
+        <v>-0.2803</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8678</v>
+        <v>3.4338</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4714</v>
+        <v>3.7356</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3044</v>
+        <v>2.4855</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8349</v>
+        <v>2.924</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4694</v>
+        <v>-0.4385</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3016</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5079</v>
+        <v>-3.5108</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8096</v>
+        <v>3.4223</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5073</v>
+        <v>1.7447</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4689</v>
+        <v>-2.3698</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9616</v>
+        <v>4.1145</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-1.8331</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.961</v>
+        <v>-1.141</v>
       </c>
       <c r="O4" t="n">
-        <v>0.152</v>
+        <v>-0.6922</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1322</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5826</v>
+        <v>-0.426</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2758</v>
+        <v>-0.1599</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3068</v>
+        <v>-0.2662</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4338</v>
+        <v>1.8678</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7356</v>
+        <v>2.4714</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="5">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.546</v>
+        <v>-0.1051</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2728</v>
+        <v>0.3573</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7269</v>
+        <v>-0.4623</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0298</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5002</v>
+        <v>0.8491</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5524</v>
+        <v>0.6369</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0522</v>
+        <v>0.2123</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3018</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0696</v>
+        <v>-0.1698</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0208</v>
+        <v>0.7285</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9512</v>
+        <v>-0.8983</v>
       </c>
       <c r="G7" t="n">
         <v>0.1473</v>
@@ -1000,13 +1000,13 @@
         <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6014</v>
+        <v>0.362</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9587</v>
+        <v>0.6664</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3574</v>
+        <v>-0.3045</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2452</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7036</v>
+        <v>-0.4739</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.525</v>
+        <v>-0.4276</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1786</v>
+        <v>-0.0463</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7207</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1716</v>
+        <v>0.0581</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.0974</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.551</v>
+        <v>-1.6593</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2574</v>
+        <v>-0.1012</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2936</v>
+        <v>-1.5581</v>
       </c>
       <c r="G9" t="n">
         <v>0.5548999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.7238</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4115</v>
+        <v>-0.2553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2039</v>
+        <v>-0.4685</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8678</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.0375</v>
+        <v>-5.1598</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1302</v>
+        <v>-1.6229</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9072</v>
+        <v>-3.5369</v>
       </c>
       <c r="G10" t="n">
         <v>-0.371</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7794</v>
+        <v>-0.9018</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9871</v>
+        <v>-0.4797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7924</v>
+        <v>-0.422</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2452</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.123900000000001</v>
+        <v>-6.9216</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.1175</v>
+        <v>-5.2591</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0065</v>
+        <v>-1.6625</v>
       </c>
       <c r="G11" t="n">
         <v>-5.625</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.5178</v>
+        <v>-1.3155</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1511</v>
+        <v>-0.2927</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3667</v>
+        <v>-1.0228</v>
       </c>
       <c r="V11" t="n">
         <v>0.9624</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4179999999999993</v>
+        <v>1.2997</v>
       </c>
       <c r="E12" t="n">
-        <v>11.7081</v>
+        <v>12.5898</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.2902</v>
+        <v>-11.29</v>
       </c>
       <c r="G12" t="n">
         <v>4.536699999999998</v>
@@ -1366,7 +1366,7 @@
         <v>15.5726</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0206</v>
+        <v>3.020600000000001</v>
       </c>
       <c r="L12" t="n">
         <v>12.552</v>
@@ -1390,13 +1390,13 @@
         <v>12.2655</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7791</v>
+        <v>-3.8974</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8437</v>
+        <v>-0.9617</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.9356</v>
+        <v>-2.9358</v>
       </c>
       <c r="V12" t="n">
         <v>0.6606</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4304</v>
+        <v>4.2588</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2044</v>
+        <v>6.0352</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.774</v>
+        <v>-1.7763</v>
       </c>
       <c r="G13" t="n">
         <v>2.3706</v>
@@ -1468,13 +1468,13 @@
         <v>2.2644</v>
       </c>
       <c r="S13" t="n">
-        <v>1.777</v>
+        <v>0.6055</v>
       </c>
       <c r="T13" t="n">
-        <v>1.543</v>
+        <v>0.3738</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2341</v>
+        <v>0.2317</v>
       </c>
       <c r="V13" t="n">
         <v>1.8488</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FERRAGUT SEBASTIA</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4405</v>
+        <v>2.6508</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8856</v>
+        <v>5.9221</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4452</v>
+        <v>-3.2713</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2251</v>
+        <v>2.7292</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9526</v>
+        <v>4.1446</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7275</v>
+        <v>-1.4155</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6167</v>
+        <v>5.1235</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6255</v>
+        <v>5.0242</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2422</v>
+        <v>0.0993</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8419</v>
+        <v>-2.3944</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3271</v>
+        <v>-0.8796</v>
       </c>
       <c r="O14" t="n">
         <v>-1.5148</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
         <v>1.6983</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9299</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3637</v>
+        <v>-0.1258</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5662</v>
+        <v>0.217</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9244</v>
+        <v>-0.9244</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7922</v>
+        <v>1.8678</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8678</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>A. FERRAGUT SEBASTIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5644</v>
+        <v>2.4632</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4606</v>
+        <v>3.5933</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8962</v>
+        <v>-1.1301</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7292</v>
+        <v>-0.2251</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1446</v>
+        <v>-1.9526</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4155</v>
+        <v>1.7275</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1235</v>
+        <v>1.6167</v>
       </c>
       <c r="K15" t="n">
-        <v>5.0242</v>
+        <v>-1.6255</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0993</v>
+        <v>3.2422</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3944</v>
+        <v>-1.8419</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8796</v>
+        <v>-0.3271</v>
       </c>
       <c r="O15" t="n">
         <v>-1.5148</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7548</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R15" t="n">
         <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9952</v>
+        <v>1.9527</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5873</v>
+        <v>1.0714</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5921</v>
+        <v>0.8813</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9244</v>
+        <v>0.9244</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8678</v>
+        <v>2.7922</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7922</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="16">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0081</v>
+        <v>-0.5357</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0281</v>
+        <v>-0.7514</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.02</v>
+        <v>0.2157</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9256</v>
@@ -1780,13 +1780,13 @@
         <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4431</v>
+        <v>1.8993</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5401</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.903</v>
+        <v>1.1387</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2642</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4119</v>
+        <v>-1.2068</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8017</v>
+        <v>1.1914</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2136</v>
+        <v>-2.3983</v>
       </c>
       <c r="G18" t="n">
         <v>-3.3881</v>
@@ -1858,13 +1858,13 @@
         <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7219</v>
+        <v>0.4832</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1851</v>
+        <v>0.5748</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.907</v>
+        <v>-0.0916</v>
       </c>
       <c r="V18" t="n">
         <v>1.8868</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5521</v>
+        <v>-2.2009</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9606</v>
+        <v>-2.7658</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4085</v>
+        <v>0.5649</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2953</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8794</v>
+        <v>-0.5282</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7642</v>
+        <v>-0.5694</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1152</v>
+        <v>0.0412</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7254</v>
+        <v>-2.5221</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0365</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6889</v>
+        <v>-1.5831</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9359</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7895</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4703</v>
+        <v>-0.3729</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3192</v>
+        <v>-0.2134</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8057</v>
+        <v>-2.6601</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.727</v>
+        <v>-1.6296</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0787</v>
+        <v>-1.0305</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5002</v>
@@ -2092,13 +2092,13 @@
         <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>2.0152</v>
+        <v>2.1608</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1257</v>
+        <v>1.2231</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8895</v>
+        <v>0.9377</v>
       </c>
       <c r="V21" t="n">
         <v>-3.132</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4177999999999997</v>
+        <v>0.8810999999999982</v>
       </c>
       <c r="E22" t="n">
-        <v>11.2902</v>
+        <v>11.2901</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.7081</v>
+        <v>-10.409</v>
       </c>
       <c r="G22" t="n">
         <v>-4.5365</v>
       </c>
       <c r="H22" t="n">
-        <v>5.204199999999999</v>
+        <v>5.2042</v>
       </c>
       <c r="I22" t="n">
-        <v>-9.7409</v>
+        <v>-9.740899999999998</v>
       </c>
       <c r="J22" t="n">
         <v>11.036</v>
@@ -2155,13 +2155,13 @@
         <v>-15.5726</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.0207</v>
+        <v>-3.020699999999999</v>
       </c>
       <c r="O22" t="n">
         <v>-12.552</v>
       </c>
       <c r="P22" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.2655</v>
@@ -2170,13 +2170,13 @@
         <v>12.2655</v>
       </c>
       <c r="S22" t="n">
-        <v>4.7792</v>
+        <v>6.0784</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9358</v>
+        <v>2.9356</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8435</v>
+        <v>3.1426</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6606000000000001</v>
